--- a/media/media-report.xlsx
+++ b/media/media-report.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="media_publications" sheetId="1" r:id="R86d79c06a0e64485"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" r:id="R5cab97e61c864732"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="media_publications" sheetId="1" r:id="R7ca34609a1d744a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" r:id="Rf57b088740ba4fe6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -578,7 +578,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1dd14a87b33e4c2a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4751d05b8880434e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -608,7 +608,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R71b13baa5e8c4185"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R557ecbee14ea4475"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -618,16 +618,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="mediapublicationsExport" displayName="mediapublicationsExport" ref="A1:G17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:G17"/>
-  <x:tableColumns count="7">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="mediapublicationsExport" displayName="mediapublicationsExport" ref="A1:F17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:F17"/>
+  <x:tableColumns count="6">
     <x:tableColumn id="1" name="id"/>
     <x:tableColumn id="2" name="publication_date"/>
     <x:tableColumn id="3" name="event_name"/>
     <x:tableColumn id="4" name="publication_format"/>
     <x:tableColumn id="5" name="channel_name"/>
     <x:tableColumn id="6" name="views"/>
-    <x:tableColumn id="7" name="data_origin"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -837,7 +836,6 @@
     <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="32" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -856,11 +854,8 @@
       <x:c r="E1" s="9" t="str">
         <x:v>channel_name</x:v>
       </x:c>
-      <x:c r="F1" s="9" t="str">
+      <x:c r="F1" s="10" t="str">
         <x:v>views</x:v>
-      </x:c>
-      <x:c r="G1" s="10" t="str">
-        <x:v>data_origin</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="23" customHeight="1">
@@ -882,9 +877,6 @@
       <x:c r="F2" s="3" t="n">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="3" ht="23" customHeight="1">
       <x:c r="A3" s="3" t="str">
@@ -905,9 +897,6 @@
       <x:c r="F3" s="3" t="n">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="G3" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
       <x:c r="A4" s="3" t="str">
@@ -928,9 +917,6 @@
       <x:c r="F4" s="3" t="n">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="G4" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="5" ht="23" customHeight="1">
       <x:c r="A5" s="3" t="str">
@@ -951,9 +937,6 @@
       <x:c r="F5" s="3" t="n">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="6" ht="23" customHeight="1">
       <x:c r="A6" s="3" t="str">
@@ -974,9 +957,6 @@
       <x:c r="F6" s="3" t="n">
         <x:v>245</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="7" ht="23" customHeight="1">
       <x:c r="A7" s="3" t="str">
@@ -997,9 +977,6 @@
       <x:c r="F7" s="3" t="n">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="G7" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="3" t="str">
@@ -1020,9 +997,6 @@
       <x:c r="F8" s="3" t="n">
         <x:v>318</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="9" ht="23" customHeight="1">
       <x:c r="A9" s="3" t="str">
@@ -1043,9 +1017,6 @@
       <x:c r="F9" s="3" t="n">
         <x:v>475</x:v>
       </x:c>
-      <x:c r="G9" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="10" ht="23" customHeight="1">
       <x:c r="A10" s="3" t="str">
@@ -1066,9 +1037,6 @@
       <x:c r="F10" s="3" t="n">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="G10" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="11" ht="23" customHeight="1">
       <x:c r="A11" s="3" t="str">
@@ -1089,9 +1057,6 @@
       <x:c r="F11" s="3" t="n">
         <x:v>427</x:v>
       </x:c>
-      <x:c r="G11" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
       <x:c r="A12" s="3" t="str">
@@ -1112,9 +1077,6 @@
       <x:c r="F12" s="3" t="n">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="G12" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="13" ht="23" customHeight="1">
       <x:c r="A13" s="3" t="str">
@@ -1135,9 +1097,6 @@
       <x:c r="F13" s="3" t="n">
         <x:v>490</x:v>
       </x:c>
-      <x:c r="G13" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="14" ht="23" customHeight="1">
       <x:c r="A14" s="3" t="str">
@@ -1158,9 +1117,6 @@
       <x:c r="F14" s="3" t="n">
         <x:v>620</x:v>
       </x:c>
-      <x:c r="G14" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
       <x:c r="A15" s="3" t="str">
@@ -1181,9 +1137,6 @@
       <x:c r="F15" s="3" t="n">
         <x:v>811</x:v>
       </x:c>
-      <x:c r="G15" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
       <x:c r="A16" s="3" t="str">
@@ -1204,9 +1157,6 @@
       <x:c r="F16" s="3" t="n">
         <x:v>438</x:v>
       </x:c>
-      <x:c r="G16" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
     <x:row r="17" ht="23" customHeight="1">
       <x:c r="A17" s="3" t="str">
@@ -1227,14 +1177,11 @@
       <x:c r="F17" s="3" t="n">
         <x:v>559</x:v>
       </x:c>
-      <x:c r="G17" s="3" t="str">
-        <x:v>modeled</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R657b3241e4114b37"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8731e376ad34a43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2098,7 +2045,7 @@
     <x:row r="40" ht="25" customHeight="1">
       <x:c r="A40" s="12"/>
       <x:c r="B40" s="27" t="str">
-        <x:v>Детальные записи смоделированы. Итоговые показатели — из презентации проекта.</x:v>
+        <x:v>Источник итоговых показателей: «Мозаика Культур 2 (1)», слайд 13.</x:v>
       </x:c>
       <x:c r="C40" s="12"/>
       <x:c r="D40" s="12"/>
@@ -2116,9 +2063,7 @@
     </x:row>
     <x:row r="41" ht="25" customHeight="1">
       <x:c r="A41" s="12"/>
-      <x:c r="B41" s="27" t="str">
-        <x:v>16 публикаций и 6 568 просмотров: слайд 13. Даты и распределения заданы в модели.</x:v>
-      </x:c>
+      <x:c r="B41" s="12"/>
       <x:c r="C41" s="12"/>
       <x:c r="D41" s="12"/>
       <x:c r="E41" s="12"/>
@@ -2186,6 +2131,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9804c03e738d4bcb"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5125a9275c364063"/>
 </x:worksheet>
 </file>